--- a/datos/paises.xlsx
+++ b/datos/paises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Desktop\Juegos\Road to Gold\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1705985B-84C3-409F-873D-0B87A0794CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7C4C63-D57F-4660-9431-28683C6A5E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C12F03E-F4F1-4B58-AEF9-00A818977629}"/>
   </bookViews>
@@ -702,7 +702,7 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -753,7 +753,7 @@
         <v>2</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>8</v>
@@ -987,7 +987,7 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -1059,7 +1059,7 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1131,7 +1131,7 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>43</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1275,7 +1275,7 @@
         <v>45</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -1347,7 +1347,7 @@
         <v>47</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -1419,7 +1419,7 @@
         <v>49</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -1563,7 +1563,7 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1635,7 +1635,7 @@
         <v>55</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -1779,7 +1779,7 @@
         <v>60</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>7</v>
@@ -1851,7 +1851,7 @@
         <v>62</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -1993,7 +1993,7 @@
         <v>68</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2064,7 +2064,7 @@
         <v>66</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21">
         <v>5</v>

--- a/datos/paises.xlsx
+++ b/datos/paises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Desktop\Juegos\Road to Gold\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7C4C63-D57F-4660-9431-28683C6A5E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6DC156-90F7-4C7A-8528-9799C2C43D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C12F03E-F4F1-4B58-AEF9-00A818977629}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="73">
   <si>
     <t>id</t>
   </si>
@@ -246,6 +246,18 @@
   </si>
   <si>
     <t>México</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>Taipei</t>
   </si>
 </sst>
 </file>
@@ -617,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259D404A-F656-47E9-B6EB-214B2E007FEA}">
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -705,7 +717,7 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -776,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>8</v>
@@ -847,7 +859,7 @@
         <v>6</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -918,7 +930,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -990,7 +1002,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -1278,7 +1290,7 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -1350,7 +1362,7 @@
         <v>2</v>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -1422,7 +1434,7 @@
         <v>7</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>8</v>
@@ -1782,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1854,7 +1866,7 @@
         <v>6</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -2067,7 +2079,7 @@
         <v>3</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -2121,6 +2133,148 @@
         <v>28</v>
       </c>
       <c r="W21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>5</v>
+      </c>
+      <c r="L22">
+        <v>3</v>
+      </c>
+      <c r="M22">
+        <v>7</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>3</v>
+      </c>
+      <c r="Q22">
+        <v>6</v>
+      </c>
+      <c r="R22">
+        <v>6</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22" t="s">
+        <v>28</v>
+      </c>
+      <c r="W22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>4</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>3</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>6</v>
+      </c>
+      <c r="U23">
+        <v>8</v>
+      </c>
+      <c r="V23" t="s">
+        <v>40</v>
+      </c>
+      <c r="W23" t="s">
         <v>3</v>
       </c>
     </row>

--- a/datos/paises.xlsx
+++ b/datos/paises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Desktop\Juegos\Road to Gold\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6DC156-90F7-4C7A-8528-9799C2C43D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCA9004-9113-46F4-882C-92CA80F65684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C12F03E-F4F1-4B58-AEF9-00A818977629}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -258,6 +258,18 @@
   </si>
   <si>
     <t>Taipei</t>
+  </si>
+  <si>
+    <t>notaRugby</t>
+  </si>
+  <si>
+    <t>notaTiroarco</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>Austria</t>
   </si>
 </sst>
 </file>
@@ -629,10 +641,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259D404A-F656-47E9-B6EB-214B2E007FEA}">
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="21" width="11.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -697,13 +712,19 @@
         <v>21</v>
       </c>
       <c r="V1" t="s">
+        <v>73</v>
+      </c>
+      <c r="W1" t="s">
+        <v>74</v>
+      </c>
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -767,14 +788,20 @@
       <c r="U2">
         <v>4</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2">
+        <v>5</v>
+      </c>
+      <c r="W2">
+        <v>5</v>
+      </c>
+      <c r="X2" t="s">
         <v>26</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -838,14 +865,20 @@
       <c r="U3">
         <v>1</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3">
+        <v>7</v>
+      </c>
+      <c r="W3">
+        <v>7</v>
+      </c>
+      <c r="X3" t="s">
         <v>28</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -909,14 +942,20 @@
       <c r="U4">
         <v>0</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>6</v>
+      </c>
+      <c r="X4" t="s">
         <v>26</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Y4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -972,7 +1011,7 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>4</v>
@@ -980,14 +1019,20 @@
       <c r="U5">
         <v>1</v>
       </c>
-      <c r="V5" t="s">
+      <c r="V5">
+        <v>8</v>
+      </c>
+      <c r="W5">
+        <v>7</v>
+      </c>
+      <c r="X5" t="s">
         <v>26</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Y5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>A5+1</f>
         <v>5</v>
@@ -1052,14 +1097,20 @@
       <c r="U6">
         <v>9</v>
       </c>
-      <c r="V6" t="s">
+      <c r="V6">
+        <v>4</v>
+      </c>
+      <c r="W6">
+        <v>7</v>
+      </c>
+      <c r="X6" t="s">
         <v>40</v>
       </c>
-      <c r="W6" t="s">
+      <c r="Y6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" ref="A7:A18" si="0">A6+1</f>
         <v>6</v>
@@ -1124,14 +1175,20 @@
       <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7" t="s">
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7" t="s">
         <v>28</v>
       </c>
-      <c r="W7" t="s">
+      <c r="Y7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1196,14 +1253,20 @@
       <c r="U8">
         <v>0</v>
       </c>
-      <c r="V8" t="s">
+      <c r="V8">
+        <v>5</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8" t="s">
         <v>41</v>
       </c>
-      <c r="W8" t="s">
+      <c r="Y8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1268,14 +1331,20 @@
       <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9" t="s">
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>2</v>
+      </c>
+      <c r="X9" t="s">
         <v>28</v>
       </c>
-      <c r="W9" t="s">
+      <c r="Y9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1332,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10">
         <v>4</v>
@@ -1340,14 +1409,20 @@
       <c r="U10">
         <v>2</v>
       </c>
-      <c r="V10" t="s">
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>6</v>
+      </c>
+      <c r="X10" t="s">
         <v>26</v>
       </c>
-      <c r="W10" t="s">
+      <c r="Y10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1404,7 +1479,7 @@
         <v>5</v>
       </c>
       <c r="S11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1412,14 +1487,20 @@
       <c r="U11">
         <v>7</v>
       </c>
-      <c r="V11" t="s">
+      <c r="V11">
+        <v>3</v>
+      </c>
+      <c r="W11">
+        <v>6</v>
+      </c>
+      <c r="X11" t="s">
         <v>40</v>
       </c>
-      <c r="W11" t="s">
+      <c r="Y11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1484,14 +1565,20 @@
       <c r="U12">
         <v>4</v>
       </c>
-      <c r="V12" t="s">
+      <c r="V12">
+        <v>8</v>
+      </c>
+      <c r="W12">
+        <v>5</v>
+      </c>
+      <c r="X12" t="s">
         <v>26</v>
       </c>
-      <c r="W12" t="s">
+      <c r="Y12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1556,14 +1643,20 @@
       <c r="U13">
         <v>8</v>
       </c>
-      <c r="V13" t="s">
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>10</v>
+      </c>
+      <c r="X13" t="s">
         <v>40</v>
       </c>
-      <c r="W13" t="s">
+      <c r="Y13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1628,14 +1721,20 @@
       <c r="U14">
         <v>0</v>
       </c>
-      <c r="V14" t="s">
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14" t="s">
         <v>41</v>
       </c>
-      <c r="W14" t="s">
+      <c r="Y14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1700,14 +1799,20 @@
       <c r="U15">
         <v>1</v>
       </c>
-      <c r="V15" t="s">
+      <c r="V15">
+        <v>9</v>
+      </c>
+      <c r="W15">
+        <v>3</v>
+      </c>
+      <c r="X15" t="s">
         <v>56</v>
       </c>
-      <c r="W15" t="s">
+      <c r="Y15" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1772,14 +1877,20 @@
       <c r="U16">
         <v>6</v>
       </c>
-      <c r="V16" t="s">
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>6</v>
+      </c>
+      <c r="X16" t="s">
         <v>40</v>
       </c>
-      <c r="W16" t="s">
+      <c r="Y16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1844,14 +1955,20 @@
       <c r="U17">
         <v>1</v>
       </c>
-      <c r="V17" t="s">
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17" t="s">
         <v>26</v>
       </c>
-      <c r="W17" t="s">
+      <c r="Y17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1896,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="O18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -1916,14 +2033,20 @@
       <c r="U18">
         <v>1</v>
       </c>
-      <c r="V18" t="s">
+      <c r="V18">
+        <v>2</v>
+      </c>
+      <c r="W18">
+        <v>6</v>
+      </c>
+      <c r="X18" t="s">
         <v>26</v>
       </c>
-      <c r="W18" t="s">
+      <c r="Y18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1987,14 +2110,20 @@
       <c r="U19">
         <v>0</v>
       </c>
-      <c r="V19" t="s">
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19" t="s">
         <v>26</v>
       </c>
-      <c r="W19" t="s">
+      <c r="Y19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2050,7 +2179,7 @@
         <v>2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
         <v>1</v>
@@ -2058,14 +2187,20 @@
       <c r="U20">
         <v>1</v>
       </c>
-      <c r="V20" t="s">
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>7</v>
+      </c>
+      <c r="X20" t="s">
         <v>28</v>
       </c>
-      <c r="W20" t="s">
+      <c r="Y20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2129,14 +2264,20 @@
       <c r="U21">
         <v>1</v>
       </c>
-      <c r="V21" t="s">
+      <c r="V21">
+        <v>2</v>
+      </c>
+      <c r="W21">
+        <v>4</v>
+      </c>
+      <c r="X21" t="s">
         <v>28</v>
       </c>
-      <c r="W21" t="s">
+      <c r="Y21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2200,14 +2341,20 @@
       <c r="U22">
         <v>0</v>
       </c>
-      <c r="V22" t="s">
+      <c r="V22">
+        <v>7</v>
+      </c>
+      <c r="W22">
+        <v>2</v>
+      </c>
+      <c r="X22" t="s">
         <v>28</v>
       </c>
-      <c r="W22" t="s">
+      <c r="Y22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2271,10 +2418,93 @@
       <c r="U23">
         <v>8</v>
       </c>
-      <c r="V23" t="s">
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>7</v>
+      </c>
+      <c r="X23" t="s">
         <v>40</v>
       </c>
-      <c r="W23" t="s">
+      <c r="Y23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>4</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>6</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>3</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>3</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>3</v>
+      </c>
+      <c r="S24">
+        <v>9</v>
+      </c>
+      <c r="T24">
+        <v>3</v>
+      </c>
+      <c r="U24">
+        <v>2</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y24" t="s">
         <v>3</v>
       </c>
     </row>

--- a/datos/paises.xlsx
+++ b/datos/paises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Desktop\Juegos\Road to Gold\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCA9004-9113-46F4-882C-92CA80F65684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37846D37-C822-406E-9136-04EBD1951DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C12F03E-F4F1-4B58-AEF9-00A818977629}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
   <si>
     <t>id</t>
   </si>
@@ -270,6 +270,18 @@
   </si>
   <si>
     <t>Austria</t>
+  </si>
+  <si>
+    <t>Fiji</t>
+  </si>
+  <si>
+    <t>FIJ</t>
+  </si>
+  <si>
+    <t>NZL</t>
+  </si>
+  <si>
+    <t>Nueva Zelanda</t>
   </si>
 </sst>
 </file>
@@ -641,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259D404A-F656-47E9-B6EB-214B2E007FEA}">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="21" width="11.42578125" customWidth="1"/>
@@ -2508,6 +2520,160 @@
         <v>3</v>
       </c>
     </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>10</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>9</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>8</v>
+      </c>
+      <c r="J26">
+        <v>6</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>10</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos/paises.xlsx
+++ b/datos/paises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Desktop\Juegos\Road to Gold\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37846D37-C822-406E-9136-04EBD1951DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845120AF-3C9A-4365-A23F-3B42CFE15A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C12F03E-F4F1-4B58-AEF9-00A818977629}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="98">
   <si>
     <t>id</t>
   </si>
@@ -282,6 +282,57 @@
   </si>
   <si>
     <t>Nueva Zelanda</t>
+  </si>
+  <si>
+    <t>perfil</t>
+  </si>
+  <si>
+    <t>pesoAparicion</t>
+  </si>
+  <si>
+    <t>grupoDesbloqueo</t>
+  </si>
+  <si>
+    <t>superpotencia</t>
+  </si>
+  <si>
+    <t>generalista</t>
+  </si>
+  <si>
+    <t>potencia_especializada</t>
+  </si>
+  <si>
+    <t>especialista</t>
+  </si>
+  <si>
+    <t>inicial</t>
+  </si>
+  <si>
+    <t>BUL</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>desafio</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>ROU</t>
+  </si>
+  <si>
+    <t>Rumanía</t>
+  </si>
+  <si>
+    <t>RSA</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
   </si>
 </sst>
 </file>
@@ -653,13 +704,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259D404A-F656-47E9-B6EB-214B2E007FEA}">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="21" width="11.42578125" customWidth="1"/>
+    <col min="4" max="23" width="11.42578125" customWidth="1"/>
+    <col min="26" max="26" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,8 +787,17 @@
       <c r="Y1" t="s">
         <v>2</v>
       </c>
+      <c r="Z1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -812,8 +873,17 @@
       <c r="Y2" t="s">
         <v>3</v>
       </c>
+      <c r="Z2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -889,8 +959,14 @@
       <c r="Y3" t="s">
         <v>3</v>
       </c>
+      <c r="Z3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -966,8 +1042,17 @@
       <c r="Y4" t="s">
         <v>3</v>
       </c>
+      <c r="Z4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1043,8 +1128,14 @@
       <c r="Y5" t="s">
         <v>3</v>
       </c>
+      <c r="Z5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>A5+1</f>
         <v>5</v>
@@ -1121,8 +1212,14 @@
       <c r="Y6" t="s">
         <v>3</v>
       </c>
+      <c r="Z6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" ref="A7:A18" si="0">A6+1</f>
         <v>6</v>
@@ -1199,8 +1296,17 @@
       <c r="Y7" t="s">
         <v>3</v>
       </c>
+      <c r="Z7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1277,8 +1383,14 @@
       <c r="Y8" t="s">
         <v>3</v>
       </c>
+      <c r="Z8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1355,8 +1467,14 @@
       <c r="Y9" t="s">
         <v>3</v>
       </c>
+      <c r="Z9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1433,8 +1551,17 @@
       <c r="Y10" t="s">
         <v>3</v>
       </c>
+      <c r="Z10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1511,8 +1638,14 @@
       <c r="Y11" t="s">
         <v>3</v>
       </c>
+      <c r="Z11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1589,8 +1722,14 @@
       <c r="Y12" t="s">
         <v>3</v>
       </c>
+      <c r="Z12" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1667,8 +1806,17 @@
       <c r="Y13" t="s">
         <v>3</v>
       </c>
+      <c r="Z13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1745,8 +1893,14 @@
       <c r="Y14" t="s">
         <v>3</v>
       </c>
+      <c r="Z14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1823,8 +1977,17 @@
       <c r="Y15" t="s">
         <v>3</v>
       </c>
+      <c r="Z15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1901,8 +2064,14 @@
       <c r="Y16" t="s">
         <v>3</v>
       </c>
+      <c r="Z16" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1979,8 +2148,14 @@
       <c r="Y17" t="s">
         <v>3</v>
       </c>
+      <c r="Z17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2057,8 +2232,14 @@
       <c r="Y18" t="s">
         <v>3</v>
       </c>
+      <c r="Z18" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2134,8 +2315,14 @@
       <c r="Y19" t="s">
         <v>3</v>
       </c>
+      <c r="Z19" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2211,8 +2398,14 @@
       <c r="Y20" t="s">
         <v>3</v>
       </c>
+      <c r="Z20" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2288,8 +2481,17 @@
       <c r="Y21" t="s">
         <v>3</v>
       </c>
+      <c r="Z21" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2365,8 +2567,17 @@
       <c r="Y22" t="s">
         <v>3</v>
       </c>
+      <c r="Z22" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2442,8 +2653,14 @@
       <c r="Y23" t="s">
         <v>3</v>
       </c>
+      <c r="Z23" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2519,8 +2736,17 @@
       <c r="Y24" t="s">
         <v>3</v>
       </c>
+      <c r="Z24" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2596,8 +2822,14 @@
       <c r="Y25" t="s">
         <v>3</v>
       </c>
+      <c r="Z25" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2672,6 +2904,347 @@
       </c>
       <c r="Y26" t="s">
         <v>3</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>5</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>2</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>6</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>2</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA27">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28">
+        <v>8</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>7</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>6</v>
+      </c>
+      <c r="J28">
+        <v>5</v>
+      </c>
+      <c r="K28">
+        <v>7</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>6</v>
+      </c>
+      <c r="N28">
+        <v>6</v>
+      </c>
+      <c r="O28">
+        <v>4</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
+      <c r="R28">
+        <v>6</v>
+      </c>
+      <c r="S28">
+        <v>2</v>
+      </c>
+      <c r="T28">
+        <v>2</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28">
+        <v>8</v>
+      </c>
+      <c r="W28">
+        <v>3</v>
+      </c>
+      <c r="X28" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29">
+        <v>9</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>4</v>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
+      <c r="P29">
+        <v>4</v>
+      </c>
+      <c r="Q29">
+        <v>2</v>
+      </c>
+      <c r="R29">
+        <v>4</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>3</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29">
+        <v>2</v>
+      </c>
+      <c r="X29" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>5</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>5</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>2</v>
+      </c>
+      <c r="S30">
+        <v>2</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30">
+        <v>8</v>
+      </c>
+      <c r="W30">
+        <v>1</v>
+      </c>
+      <c r="X30" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA30">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/datos/paises.xlsx
+++ b/datos/paises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Desktop\Juegos\Road to Gold\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845120AF-3C9A-4365-A23F-3B42CFE15A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1E8063-3286-404F-AD57-8AECF7C2AB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C12F03E-F4F1-4B58-AEF9-00A818977629}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="100">
   <si>
     <t>id</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>Sudáfrica</t>
+  </si>
+  <si>
+    <t>CZE</t>
+  </si>
+  <si>
+    <t>República Checa</t>
   </si>
 </sst>
 </file>
@@ -704,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259D404A-F656-47E9-B6EB-214B2E007FEA}">
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="23" width="11.42578125" customWidth="1"/>
@@ -3247,6 +3253,86 @@
         <v>1</v>
       </c>
     </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>8</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31">
+        <v>5</v>
+      </c>
+      <c r="L31">
+        <v>6</v>
+      </c>
+      <c r="M31">
+        <v>2</v>
+      </c>
+      <c r="N31">
+        <v>4</v>
+      </c>
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="Q31">
+        <v>5</v>
+      </c>
+      <c r="R31">
+        <v>9</v>
+      </c>
+      <c r="S31">
+        <v>7</v>
+      </c>
+      <c r="T31">
+        <v>2</v>
+      </c>
+      <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos/paises.xlsx
+++ b/datos/paises.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Desktop\Juegos\Road to Gold\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1E8063-3286-404F-AD57-8AECF7C2AB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DBF1FC-4D75-4900-91A7-736CB05CA12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C12F03E-F4F1-4B58-AEF9-00A818977629}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,95 +28,122 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="103">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>codigo</t>
+  </si>
+  <si>
     <t>nombre</t>
   </si>
   <si>
+    <t>notaAtletismo</t>
+  </si>
+  <si>
+    <t>notaNatacion</t>
+  </si>
+  <si>
+    <t>notaGimnasia</t>
+  </si>
+  <si>
+    <t>notaRemo</t>
+  </si>
+  <si>
+    <t>notaBoxeo</t>
+  </si>
+  <si>
+    <t>notaPiraguismo</t>
+  </si>
+  <si>
+    <t>notaCiclismo</t>
+  </si>
+  <si>
+    <t>notaJudo</t>
+  </si>
+  <si>
+    <t>notaTiro</t>
+  </si>
+  <si>
+    <t>notaFutbol</t>
+  </si>
+  <si>
+    <t>notaBaloncesto</t>
+  </si>
+  <si>
+    <t>notaWaterpolo</t>
+  </si>
+  <si>
+    <t>notaBalonmano</t>
+  </si>
+  <si>
+    <t>notaVoleibol</t>
+  </si>
+  <si>
+    <t>notaTenis</t>
+  </si>
+  <si>
+    <t>notaEscalada</t>
+  </si>
+  <si>
+    <t>notaTenismesa</t>
+  </si>
+  <si>
+    <t>notaBadminton</t>
+  </si>
+  <si>
+    <t>notaRugby</t>
+  </si>
+  <si>
+    <t>notaTiroarco</t>
+  </si>
+  <si>
+    <t>notaHockey</t>
+  </si>
+  <si>
+    <t>notaEsgrima</t>
+  </si>
+  <si>
+    <t>continente</t>
+  </si>
+  <si>
     <t>activo</t>
   </si>
   <si>
+    <t>perfil</t>
+  </si>
+  <si>
+    <t>pesoAparicion</t>
+  </si>
+  <si>
+    <t>grupoDesbloqueo</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>Europa</t>
+  </si>
+  <si>
     <t>true</t>
   </si>
   <si>
-    <t>codigo</t>
-  </si>
-  <si>
-    <t>notaAtletismo</t>
-  </si>
-  <si>
-    <t>notaNatacion</t>
-  </si>
-  <si>
-    <t>notaGimnasia</t>
-  </si>
-  <si>
-    <t>notaRemo</t>
-  </si>
-  <si>
-    <t>notaBoxeo</t>
-  </si>
-  <si>
-    <t>notaPiraguismo</t>
-  </si>
-  <si>
-    <t>notaCiclismo</t>
-  </si>
-  <si>
-    <t>notaJudo</t>
-  </si>
-  <si>
-    <t>notaTiro</t>
-  </si>
-  <si>
-    <t>notaFutbol</t>
-  </si>
-  <si>
-    <t>notaBaloncesto</t>
-  </si>
-  <si>
-    <t>notaWaterpolo</t>
-  </si>
-  <si>
-    <t>notaBalonmano</t>
-  </si>
-  <si>
-    <t>notaVoleibol</t>
-  </si>
-  <si>
-    <t>notaTenis</t>
-  </si>
-  <si>
-    <t>notaTenismesa</t>
-  </si>
-  <si>
-    <t>notaBadminton</t>
-  </si>
-  <si>
-    <t>continente</t>
-  </si>
-  <si>
-    <t>notaEscalada</t>
-  </si>
-  <si>
-    <t>ESP</t>
-  </si>
-  <si>
-    <t>España</t>
-  </si>
-  <si>
-    <t>Europa</t>
+    <t>generalista</t>
+  </si>
+  <si>
+    <t>inicial</t>
+  </si>
+  <si>
+    <t>USA</t>
   </si>
   <si>
     <t>Estados Unidos</t>
@@ -128,42 +152,45 @@
     <t>América</t>
   </si>
   <si>
+    <t>superpotencia</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
     <t>Italia</t>
   </si>
   <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>ITA</t>
+    <t>FRA</t>
   </si>
   <si>
     <t>Francia</t>
   </si>
   <si>
-    <t>FRA</t>
+    <t>CHN</t>
   </si>
   <si>
     <t>China</t>
   </si>
   <si>
-    <t>CHN</t>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>JAM</t>
   </si>
   <si>
     <t>Jamaica</t>
   </si>
   <si>
-    <t>JAM</t>
+    <t>especialista</t>
+  </si>
+  <si>
+    <t>KEN</t>
   </si>
   <si>
     <t>Kenia</t>
   </si>
   <si>
-    <t>KEN</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
     <t>África</t>
   </si>
   <si>
@@ -173,6 +200,9 @@
     <t>Cuba</t>
   </si>
   <si>
+    <t>potencia_especializada</t>
+  </si>
+  <si>
     <t>GER</t>
   </si>
   <si>
@@ -236,18 +266,21 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>desafio</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
     <t>BRA</t>
   </si>
   <si>
     <t>Brasil</t>
   </si>
   <si>
-    <t>MEX</t>
-  </si>
-  <si>
-    <t>México</t>
-  </si>
-  <si>
     <t>ARG</t>
   </si>
   <si>
@@ -260,63 +293,30 @@
     <t>Taipei</t>
   </si>
   <si>
-    <t>notaRugby</t>
-  </si>
-  <si>
-    <t>notaTiroarco</t>
-  </si>
-  <si>
     <t>AUT</t>
   </si>
   <si>
     <t>Austria</t>
   </si>
   <si>
+    <t>FIJ</t>
+  </si>
+  <si>
     <t>Fiji</t>
   </si>
   <si>
-    <t>FIJ</t>
-  </si>
-  <si>
     <t>NZL</t>
   </si>
   <si>
     <t>Nueva Zelanda</t>
   </si>
   <si>
-    <t>perfil</t>
-  </si>
-  <si>
-    <t>pesoAparicion</t>
-  </si>
-  <si>
-    <t>grupoDesbloqueo</t>
-  </si>
-  <si>
-    <t>superpotencia</t>
-  </si>
-  <si>
-    <t>generalista</t>
-  </si>
-  <si>
-    <t>potencia_especializada</t>
-  </si>
-  <si>
-    <t>especialista</t>
-  </si>
-  <si>
-    <t>inicial</t>
-  </si>
-  <si>
     <t>BUL</t>
   </si>
   <si>
     <t>Bulgaria</t>
   </si>
   <si>
-    <t>desafio</t>
-  </si>
-  <si>
     <t>CAN</t>
   </si>
   <si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>República Checa</t>
+  </si>
+  <si>
+    <t>notaSaltos</t>
   </si>
 </sst>
 </file>
@@ -709,109 +712,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259D404A-F656-47E9-B6EB-214B2E007FEA}">
-  <dimension ref="A1:AB31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="23" width="11.42578125" customWidth="1"/>
-    <col min="26" max="26" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" customWidth="1"/>
+    <col min="25" max="26" width="11.42578125" customWidth="1"/>
+    <col min="29" max="29" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" t="s">
-        <v>73</v>
-      </c>
-      <c r="W1" t="s">
-        <v>74</v>
-      </c>
-      <c r="X1" t="s">
-        <v>22</v>
-      </c>
       <c r="Y1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AA1" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="AB1" t="s">
-        <v>83</v>
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -873,31 +887,40 @@
       <c r="W2">
         <v>5</v>
       </c>
-      <c r="X2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA2">
-        <v>1</v>
+      <c r="X2">
+        <v>6</v>
+      </c>
+      <c r="Y2">
+        <v>5</v>
+      </c>
+      <c r="Z2">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>32</v>
       </c>
       <c r="AB2" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -959,28 +982,37 @@
       <c r="W3">
         <v>7</v>
       </c>
-      <c r="X3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA3">
+      <c r="X3">
+        <v>3</v>
+      </c>
+      <c r="Y3">
+        <v>8</v>
+      </c>
+      <c r="Z3">
+        <v>7</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -1042,31 +1074,40 @@
       <c r="W4">
         <v>6</v>
       </c>
-      <c r="X4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA4">
-        <v>1</v>
+      <c r="X4">
+        <v>2</v>
+      </c>
+      <c r="Y4">
+        <v>9</v>
+      </c>
+      <c r="Z4">
+        <v>6</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>32</v>
       </c>
       <c r="AB4" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1128,29 +1169,38 @@
       <c r="W5">
         <v>7</v>
       </c>
-      <c r="X5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA5">
+      <c r="X5">
+        <v>3</v>
+      </c>
+      <c r="Y5">
+        <v>9</v>
+      </c>
+      <c r="Z5">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f>A5+1</f>
+        <f t="shared" ref="A6:A18" si="0">A5+1</f>
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1212,29 +1262,38 @@
       <c r="W6">
         <v>7</v>
       </c>
-      <c r="X6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA6">
+      <c r="X6">
+        <v>5</v>
+      </c>
+      <c r="Y6">
+        <v>6</v>
+      </c>
+      <c r="Z6">
+        <v>10</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" ref="A7:A18" si="0">A6+1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -1296,32 +1355,41 @@
       <c r="W7">
         <v>0</v>
       </c>
-      <c r="X7" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>38</v>
       </c>
       <c r="AB7" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1383,29 +1451,38 @@
       <c r="W8">
         <v>0</v>
       </c>
-      <c r="X8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA8">
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1467,29 +1544,38 @@
       <c r="W9">
         <v>2</v>
       </c>
-      <c r="X9" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA9">
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>3</v>
+      </c>
+      <c r="Z9">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1551,32 +1637,41 @@
       <c r="W10">
         <v>6</v>
       </c>
-      <c r="X10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA10">
-        <v>1</v>
+      <c r="X10">
+        <v>9</v>
+      </c>
+      <c r="Y10">
+        <v>5</v>
+      </c>
+      <c r="Z10">
+        <v>5</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>32</v>
       </c>
       <c r="AB10" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1638,29 +1733,38 @@
       <c r="W11">
         <v>6</v>
       </c>
-      <c r="X11" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA11">
+      <c r="X11">
+        <v>3</v>
+      </c>
+      <c r="Y11">
+        <v>8</v>
+      </c>
+      <c r="Z11">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -1722,29 +1826,38 @@
       <c r="W12">
         <v>5</v>
       </c>
-      <c r="X12" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA12">
+      <c r="X12">
+        <v>7</v>
+      </c>
+      <c r="Y12">
+        <v>3</v>
+      </c>
+      <c r="Z12">
+        <v>8</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1806,116 +1919,134 @@
       <c r="W13">
         <v>10</v>
       </c>
-      <c r="X13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA13">
-        <v>1</v>
+      <c r="X13">
+        <v>4</v>
+      </c>
+      <c r="Y13">
+        <v>7</v>
+      </c>
+      <c r="Z13">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>46</v>
       </c>
       <c r="AB13" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="s">
         <v>52</v>
       </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14">
-        <v>6</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>1</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA14">
+      <c r="AB14" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1977,32 +2108,41 @@
       <c r="W15">
         <v>3</v>
       </c>
-      <c r="X15" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA15">
-        <v>1</v>
+      <c r="X15">
+        <v>8</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>7</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>68</v>
       </c>
       <c r="AB15" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2064,29 +2204,38 @@
       <c r="W16">
         <v>6</v>
       </c>
-      <c r="X16" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA16">
+      <c r="X16">
+        <v>7</v>
+      </c>
+      <c r="Y16">
+        <v>2</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2148,29 +2297,38 @@
       <c r="W17">
         <v>1</v>
       </c>
-      <c r="X17" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA17">
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>8</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D18">
         <v>6</v>
@@ -2232,28 +2390,37 @@
       <c r="W18">
         <v>6</v>
       </c>
-      <c r="X18" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA18">
+      <c r="X18">
+        <v>10</v>
+      </c>
+      <c r="Y18">
+        <v>3</v>
+      </c>
+      <c r="Z18">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2315,28 +2482,37 @@
       <c r="W19">
         <v>0</v>
       </c>
-      <c r="X19" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA19">
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2398,28 +2574,37 @@
       <c r="W20">
         <v>7</v>
       </c>
-      <c r="X20" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA20">
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>2</v>
+      </c>
+      <c r="Z20">
+        <v>8</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -2481,31 +2666,40 @@
       <c r="W21">
         <v>4</v>
       </c>
-      <c r="X21" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA21">
-        <v>1</v>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>4</v>
+      </c>
+      <c r="Z21">
+        <v>2</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>38</v>
       </c>
       <c r="AB21" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2567,31 +2761,40 @@
       <c r="W22">
         <v>2</v>
       </c>
-      <c r="X22" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA22">
-        <v>1</v>
+      <c r="X22">
+        <v>8</v>
+      </c>
+      <c r="Y22">
+        <v>2</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>38</v>
       </c>
       <c r="AB22" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2653,28 +2856,37 @@
       <c r="W23">
         <v>7</v>
       </c>
-      <c r="X23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA23">
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>2</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -2736,31 +2948,40 @@
       <c r="W24">
         <v>1</v>
       </c>
-      <c r="X24" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA24">
-        <v>1</v>
+      <c r="X24">
+        <v>2</v>
+      </c>
+      <c r="Y24">
+        <v>3</v>
+      </c>
+      <c r="Z24">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>32</v>
       </c>
       <c r="AB24" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2822,28 +3043,37 @@
       <c r="W25">
         <v>0</v>
       </c>
-      <c r="X25" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA25">
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -2905,28 +3135,37 @@
       <c r="W26">
         <v>0</v>
       </c>
-      <c r="X26" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA26">
+      <c r="X26">
+        <v>5</v>
+      </c>
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <v>3</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2988,31 +3227,40 @@
       <c r="W27">
         <v>0</v>
       </c>
-      <c r="X27" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA27">
-        <v>1</v>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>2</v>
+      </c>
+      <c r="Z27">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>32</v>
       </c>
       <c r="AB27" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD27">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D28">
         <v>7</v>
@@ -3074,28 +3322,37 @@
       <c r="W28">
         <v>3</v>
       </c>
-      <c r="X28" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA28">
+      <c r="X28">
+        <v>2</v>
+      </c>
+      <c r="Y28">
+        <v>5</v>
+      </c>
+      <c r="Z28">
+        <v>6</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -3157,28 +3414,37 @@
       <c r="W29">
         <v>2</v>
       </c>
-      <c r="X29" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA29">
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>6</v>
+      </c>
+      <c r="Z29">
+        <v>2</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -3240,28 +3506,37 @@
       <c r="W30">
         <v>1</v>
       </c>
-      <c r="X30" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA30">
+      <c r="X30">
+        <v>3</v>
+      </c>
+      <c r="Y30">
+        <v>1</v>
+      </c>
+      <c r="Z30">
+        <v>2</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -3323,14 +3598,26 @@
       <c r="W31">
         <v>1</v>
       </c>
-      <c r="X31" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>86</v>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>5</v>
+      </c>
+      <c r="Z31">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD31">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
